--- a/manuscript_v5/SI/S6_Table.xlsx
+++ b/manuscript_v5/SI/S6_Table.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S6 Table. Within-TCGA cross-label AUC (A5): pooled out-of-fold AUC for each training label, test label, model and repeat; means and ranges; and the pre-specified decision rule with its outcome (verbatim from the analysis summary).</t>
+          <t>S6 Table. Within-TCGA cross-label AUC (A5): pooled out-of-fold AUC for each training label, test label, model and repeat; means and ranges; and the pre-specified decision rule with its outcome (verbatim from the analysis summary). After external review this all-patients analysis is reported as descriptive only; the controlled same-patient comparison (A16) is in S1 Text.</t>
         </is>
       </c>
     </row>

--- a/manuscript_v5/SI/S6_Table.xlsx
+++ b/manuscript_v5/SI/S6_Table.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S6 Table. Within-TCGA cross-label AUC (A5): pooled out-of-fold AUC for each training label, test label, model and repeat; means and ranges; and the pre-specified decision rule with its outcome (verbatim from the analysis summary). After external review this all-patients analysis is reported as descriptive only; the controlled same-patient comparison (A16) is in S1 Text.</t>
+          <t>S6 Table. Within-TCGA cross-label AUC (A5): pooled out-of-fold AUC for each training label, test label, model and repeat; means and ranges; and the pre-specified decision rule with its outcome (verbatim from the analysis summary). In a later revision this all-patients analysis is reported as descriptive only; the controlled same-patient comparison (A16) is in S1 Text.</t>
         </is>
       </c>
     </row>
